--- a/BOM_ORGO-15_P1.xlsx
+++ b/BOM_ORGO-15_P1.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F247CB22-4EC0-4C5E-9811-61E3C1056B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F688345-95FF-4256-9F99-960899AE56C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{EEE73C29-3BDB-49EB-9C57-2FAD514C20AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Background_info" sheetId="2" state="hidden" r:id="rId1"/>
     <sheet name="Main_Table" sheetId="1" r:id="rId2"/>
+    <sheet name="Totals" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>#</t>
   </si>
@@ -171,20 +172,38 @@
     <t>5days?</t>
   </si>
   <si>
-    <t>CF tube that connects the wing tubes together (500mm)</t>
-  </si>
-  <si>
     <t>Main CF tube that would run along the wing and fuselage structure (1000mm)</t>
   </si>
   <si>
     <t>CF tube that would run along the V-tail (1000mm)</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005008563841954.html?spm=a2g0o.productlist.main.3.b0aaJRc9JRc9IJ&amp;algo_pvid=51e86ca4-3a40-4670-b78f-9a18ffbdf720&amp;algo_exp_id=51e86ca4-3a40-4670-b78f-9a18ffbdf720-2&amp;pdp_ext_f=%7B%22order%22%3A%2260%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21BGN%2121.75%2118.38%21%21%2187.00%2173.52%21%402103128917805974287168002e4048%2112000047147089281%21sea%21BG%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3Ad5d25ef1%3Bm03_new_user%3A-29895%3BpisId%3A5000000204855994&amp;curPageLogUid=dChSXGxbpe9S&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005008563841954%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>CF tube that connects the wing tubes together (1000mm)</t>
+  </si>
+  <si>
+    <t>Only 200mm needed</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/4000193051211.html?spm=a2g0o.productlist.main.5.540aHWXPHWXPps&amp;algo_pvid=0dbf6731-5a6e-4355-856a-ea1a08c92cb2&amp;algo_exp_id=0dbf6731-5a6e-4355-856a-ea1a08c92cb2-4&amp;pdp_ext_f=%7B%22order%22%3A%228%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21BGN%2155.57%2152.18%21%21%2132.99%2130.98%21%402101d49617805996051283277ec765%2110000000754935441%21sea%21BG%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3Ad5d25ef1%3Bm03_new_user%3A-29895%3BpisId%3A5000000204855994&amp;curPageLogUid=8PNFEmkJAiAB&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A4000193051211%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>30days</t>
+  </si>
+  <si>
+    <t>20days</t>
+  </si>
+  <si>
+    <t>Under development</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,8 +235,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -233,6 +260,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,7 +298,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -274,7 +307,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -305,6 +337,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -652,13 +690,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
     </row>
@@ -760,7 +798,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="57.77734375" style="2" customWidth="1"/>
     <col min="4" max="4" width="25.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8.88671875" style="1"/>
@@ -769,691 +807,712 @@
     <col min="9" max="9" width="12.21875" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.88671875" style="1"/>
-    <col min="12" max="12" width="32.21875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="32.21875" style="17" customWidth="1"/>
     <col min="13" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="7"/>
+      <c r="C1" s="6"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="16">
+      <c r="A3" s="15">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16">
+      <c r="E3" s="15"/>
+      <c r="F3" s="15">
         <v>1</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="15" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="16">
+      <c r="I3" s="15">
         <f>F3*E3</f>
         <v>0</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="4"/>
+      <c r="L3" s="16"/>
     </row>
     <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="16">
+      <c r="A4" s="15">
         <v>2</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="15">
+        <v>14.77</v>
+      </c>
+      <c r="F4" s="15">
+        <v>2</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="shared" ref="I4:I32" si="0">F4*E4</f>
+        <v>29.54</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="16"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="15">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16">
+      <c r="E5" s="15">
+        <v>31.02</v>
+      </c>
+      <c r="F5" s="15">
         <v>2</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="16">
-        <f t="shared" ref="I4:I32" si="0">F4*E4</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16" t="s">
+      <c r="H5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="0"/>
+        <v>62.04</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="16">
-        <v>3</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="14" t="s">
+      <c r="L5" s="16"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="15">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="15">
+        <v>18.22</v>
+      </c>
+      <c r="F6" s="15">
+        <v>1</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="I6" s="15">
+        <f t="shared" si="0"/>
+        <v>18.22</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="15">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="15">
+        <v>47.5</v>
+      </c>
+      <c r="F7" s="15">
+        <v>1</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="0"/>
+        <v>47.5</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="16"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="15">
+        <v>6</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="15"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="16"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="15">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="15"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="16"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="15">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="15"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="16"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="15">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="16"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="15">
+        <v>10</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="15"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="16"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="15">
+        <v>11</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="16"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="15">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="16"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="15"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="16"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="15">
+        <v>14</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="15"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="16"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="15">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="16"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="15">
+        <v>16</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="15"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="16"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="15">
+        <v>17</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="16"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="15">
+        <v>18</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="16"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="15">
+        <v>19</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="15"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="16"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="15">
+        <v>20</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="15"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="16"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="15">
+        <v>21</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="15"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="16"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="15">
+        <v>22</v>
+      </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="15">
+        <f>F24*E24</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="15"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="16"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="15">
+        <v>23</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="15"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="16"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="15">
         <v>24</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16">
-        <v>2</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
-        <v>4</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16">
-        <v>1</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="16">
-        <v>5</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="16" t="s">
+      <c r="B26" s="14"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="15"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="16"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="15">
+        <v>25</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="15"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="16"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="15">
+        <v>26</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="15"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="16"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="15">
+        <v>27</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="15"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="16"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="15">
+        <v>28</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="15"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="16"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="15">
         <v>29</v>
       </c>
-      <c r="E7" s="16">
-        <v>47.5</v>
-      </c>
-      <c r="F7" s="16">
-        <v>1</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="16">
-        <f t="shared" si="0"/>
-        <v>47.5</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="4"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="16">
-        <v>6</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="16">
-        <v>7</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="16">
-        <v>8</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="4"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="16">
-        <v>9</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="4"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="16">
-        <v>10</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="4"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="16">
-        <v>11</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="4"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="16">
-        <v>12</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="4"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="16">
-        <v>13</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="4"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="16">
-        <v>15</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="4"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="16">
-        <v>16</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="4"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="16">
-        <v>17</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="4"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="16">
-        <v>18</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="4"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="16">
-        <v>19</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="4"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="16">
-        <v>20</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="4"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="16">
-        <v>21</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="4"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="16">
-        <v>22</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="16">
-        <f>F24*E24</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="4"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="16">
-        <v>23</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="4"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="16">
-        <v>24</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="16">
-        <v>25</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="4"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="16">
-        <v>26</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="4"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="16">
-        <v>27</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="4"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="16">
-        <v>28</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="4"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="16">
-        <v>29</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="4"/>
+      <c r="I31" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="15"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="16"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="16">
+      <c r="A32" s="15">
         <v>30</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="4"/>
+      <c r="I32" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="15"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K3:K32">
@@ -1465,6 +1524,7 @@
     <hyperlink ref="H7" r:id="rId1" xr:uid="{45F219EB-CA0E-46B2-B5AC-321500547349}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -1490,4 +1550,19 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F602BA-A80C-4BEA-8ECF-F81C395286C3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/BOM_ORGO-15_P1.xlsx
+++ b/BOM_ORGO-15_P1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F688345-95FF-4256-9F99-960899AE56C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE9D731-1C25-433C-8FCE-C380CA333FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{EEE73C29-3BDB-49EB-9C57-2FAD514C20AA}"/>
   </bookViews>
@@ -37,8 +37,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={FC7EAD15-5036-416E-B513-A56CC16EB152}</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{FC7EAD15-5036-416E-B513-A56CC16EB152}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Should be 14x12</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="55">
   <si>
     <t>#</t>
   </si>
@@ -197,13 +215,19 @@
   </si>
   <si>
     <t>Under development</t>
+  </si>
+  <si>
+    <t>CF Tube 6x4mm</t>
+  </si>
+  <si>
+    <t>Smaller CF tube that runs along the wing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,8 +267,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -266,6 +296,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -298,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -343,6 +379,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -364,6 +406,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Nikolov, Aleksandar" id="{47DC221D-ABEF-4119-BAB4-8C611EFC78D8}" userId="S::anikolov5@sensata.com::11a41fcd-3703-42fb-8970-2f070df26411" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -681,6 +729,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B5" dT="2026-06-07T15:24:27.30" personId="{47DC221D-ABEF-4119-BAB4-8C611EFC78D8}" id="{FC7EAD15-5036-416E-B513-A56CC16EB152}">
+    <text>Should be 14x12</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B02F099F-610B-4C2F-A80F-3888BDD56E8E}">
   <dimension ref="B2:D14"/>
@@ -793,7 +849,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E734346-BCBC-4D9C-B399-F93315446069}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E734346-BCBC-4D9C-B399-F93315446069}">
   <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -930,10 +986,10 @@
       <c r="A5" s="15">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="21" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="15" t="s">
@@ -1043,9 +1099,15 @@
       <c r="A8" s="15">
         <v>6</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="15"/>
+      <c r="B8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>24</v>
+      </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -1525,6 +1587,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">

--- a/BOM_ORGO-15_P1.xlsx
+++ b/BOM_ORGO-15_P1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE9D731-1C25-433C-8FCE-C380CA333FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C913D6-7939-4FAA-B19F-B0AE4286CC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{EEE73C29-3BDB-49EB-9C57-2FAD514C20AA}"/>
   </bookViews>
@@ -37,24 +37,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={FC7EAD15-5036-416E-B513-A56CC16EB152}</author>
-  </authors>
-  <commentList>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{FC7EAD15-5036-416E-B513-A56CC16EB152}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Should be 14x12</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="55">
   <si>
@@ -172,12 +154,6 @@
     <t>CF Tube 22x20mm</t>
   </si>
   <si>
-    <t>CF Tube 16x14mm</t>
-  </si>
-  <si>
-    <t>CF Tube 24x22mm</t>
-  </si>
-  <si>
     <t>PA6+CF filament</t>
   </si>
   <si>
@@ -221,13 +197,19 @@
   </si>
   <si>
     <t>Smaller CF tube that runs along the wing</t>
+  </si>
+  <si>
+    <t>CF Tube 20x18mm</t>
+  </si>
+  <si>
+    <t>CF Tube 14x12mm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,14 +249,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -296,12 +272,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -334,7 +304,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -379,12 +349,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -409,9 +373,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Nikolov, Aleksandar" id="{47DC221D-ABEF-4119-BAB4-8C611EFC78D8}" userId="S::anikolov5@sensata.com::11a41fcd-3703-42fb-8970-2f070df26411" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -729,14 +691,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B5" dT="2026-06-07T15:24:27.30" personId="{47DC221D-ABEF-4119-BAB4-8C611EFC78D8}" id="{FC7EAD15-5036-416E-B513-A56CC16EB152}">
-    <text>Should be 14x12</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B02F099F-610B-4C2F-A80F-3888BDD56E8E}">
   <dimension ref="B2:D14"/>
@@ -849,7 +803,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E734346-BCBC-4D9C-B399-F93315446069}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E734346-BCBC-4D9C-B399-F93315446069}">
   <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -953,7 +907,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>24</v>
@@ -968,14 +922,14 @@
         <v>4</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I4" s="15">
         <f t="shared" ref="I4:I32" si="0">F4*E4</f>
         <v>29.54</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K4" s="18" t="s">
         <v>36</v>
@@ -986,11 +940,11 @@
       <c r="A5" s="15">
         <v>3</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>45</v>
+      <c r="B5" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>24</v>
@@ -1005,14 +959,14 @@
         <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I5" s="15">
         <f t="shared" si="0"/>
         <v>62.04</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K5" s="18" t="s">
         <v>36</v>
@@ -1024,10 +978,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>24</v>
@@ -1042,20 +996,20 @@
         <v>4</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I6" s="15">
         <f t="shared" si="0"/>
         <v>18.22</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K6" s="18" t="s">
         <v>36</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -1063,10 +1017,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>29</v>
@@ -1081,14 +1035,14 @@
         <v>4</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
         <v>47.5</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K7" s="18" t="s">
         <v>36</v>
@@ -1100,10 +1054,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>24</v>
@@ -1587,7 +1541,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -1622,7 +1575,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
